--- a/sample/demo-bill.xlsx
+++ b/sample/demo-bill.xlsx
@@ -545,7 +545,7 @@
         <v>支付成功</v>
       </c>
       <c r="I19" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000000</v>
       </c>
       <c r="J19" t="str">
         <v>H560000000000</v>
@@ -580,7 +580,7 @@
         <v>支付成功</v>
       </c>
       <c r="I20" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000001</v>
       </c>
       <c r="J20" t="str">
         <v>H560000000001</v>
@@ -615,7 +615,7 @@
         <v>已存入零钱</v>
       </c>
       <c r="I21" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000002</v>
       </c>
       <c r="J21" t="str">
         <v>H560000000002</v>
@@ -650,7 +650,7 @@
         <v>支付成功</v>
       </c>
       <c r="I22" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000003</v>
       </c>
       <c r="J22" t="str">
         <v>H560000000003</v>
@@ -685,7 +685,7 @@
         <v>支付成功</v>
       </c>
       <c r="I23" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000004</v>
       </c>
       <c r="J23" t="str">
         <v>H560000000004</v>
@@ -720,7 +720,7 @@
         <v>已存入零钱</v>
       </c>
       <c r="I24" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000005</v>
       </c>
       <c r="J24" t="str">
         <v>H560000000005</v>
@@ -755,7 +755,7 @@
         <v>支付成功</v>
       </c>
       <c r="I25" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000006</v>
       </c>
       <c r="J25" t="str">
         <v>H560000000006</v>
@@ -790,7 +790,7 @@
         <v>支付成功</v>
       </c>
       <c r="I26" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000007</v>
       </c>
       <c r="J26" t="str">
         <v>H560000000007</v>
@@ -825,7 +825,7 @@
         <v>还款成功</v>
       </c>
       <c r="I27" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000008</v>
       </c>
       <c r="J27" t="str">
         <v>H560000000008</v>
@@ -860,7 +860,7 @@
         <v>支付成功</v>
       </c>
       <c r="I28" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000009</v>
       </c>
       <c r="J28" t="str">
         <v>H560000000009</v>
@@ -895,7 +895,7 @@
         <v>支付成功</v>
       </c>
       <c r="I29" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000010</v>
       </c>
       <c r="J29" t="str">
         <v>H560000000010</v>
@@ -930,7 +930,7 @@
         <v>已存入零钱</v>
       </c>
       <c r="I30" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000011</v>
       </c>
       <c r="J30" t="str">
         <v>H560000000011</v>
@@ -965,7 +965,7 @@
         <v>支付成功</v>
       </c>
       <c r="I31" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000012</v>
       </c>
       <c r="J31" t="str">
         <v>H560000000012</v>
@@ -1000,7 +1000,7 @@
         <v>已退款</v>
       </c>
       <c r="I32" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000013</v>
       </c>
       <c r="J32" t="str">
         <v>H560000000013</v>
@@ -1035,7 +1035,7 @@
         <v>支付成功</v>
       </c>
       <c r="I33" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000014</v>
       </c>
       <c r="J33" t="str">
         <v>H560000000014</v>
@@ -1070,7 +1070,7 @@
         <v>提现已到账</v>
       </c>
       <c r="I34" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000015</v>
       </c>
       <c r="J34" t="str">
         <v>H560000000015</v>
@@ -1105,7 +1105,7 @@
         <v>支付成功</v>
       </c>
       <c r="I35" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000016</v>
       </c>
       <c r="J35" t="str">
         <v>H560000000016</v>
@@ -1140,7 +1140,7 @@
         <v>支付成功</v>
       </c>
       <c r="I36" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000017</v>
       </c>
       <c r="J36" t="str">
         <v>H560000000017</v>
@@ -1175,7 +1175,7 @@
         <v>支付成功</v>
       </c>
       <c r="I37" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000018</v>
       </c>
       <c r="J37" t="str">
         <v>H560000000018</v>
@@ -1210,7 +1210,7 @@
         <v>已存入零钱</v>
       </c>
       <c r="I38" t="str">
-        <v>42000100000000000000000000</v>
+        <v>4200000000000000000000000019</v>
       </c>
       <c r="J38" t="str">
         <v>H560000000019</v>
